--- a/ユースケース.xlsx
+++ b/ユースケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toyotajp-my.sharepoint.com/personal/1564602_tmc_twfr_toyota_co_jp/Documents/ダウンロード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C53D45-4FF8-4C56-9FE2-67556C2EFDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{F9C53D45-4FF8-4C56-9FE2-67556C2EFDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E4CF14-D159-4067-A7C6-2E765C4D5DBE}"/>
   <bookViews>
-    <workbookView xWindow="-2850" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース" sheetId="1" r:id="rId1"/>
@@ -37,31 +37,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
   <si>
     <t>外部監視</t>
     <rPh sb="0" eb="4">
       <t>ガイブカンシ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユースケース</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>指令</t>
     <rPh sb="0" eb="2">
       <t>シレイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>球体</t>
     <rPh sb="0" eb="2">
       <t>キュウタイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動許可を出す</t>
@@ -74,14 +74,14 @@
     <rPh sb="5" eb="6">
       <t>ダ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実装先</t>
     <rPh sb="0" eb="3">
       <t>ジッソウサキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動許可信号を出力</t>
@@ -97,7 +97,7 @@
     <rPh sb="7" eb="9">
       <t>シュツリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動禁止を出す</t>
@@ -110,7 +110,7 @@
     <rPh sb="5" eb="6">
       <t>ダ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動禁止信号を出力</t>
@@ -126,7 +126,7 @@
     <rPh sb="7" eb="9">
       <t>シュツリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動許可信号を受信する</t>
@@ -142,7 +142,7 @@
     <rPh sb="7" eb="9">
       <t>ジュシン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動許可信号が来たらジョイスティック操作を受け付けるようにする</t>
@@ -167,7 +167,7 @@
     <rPh sb="23" eb="24">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>駆動禁止信号が来たらジョイスティック操作を受け付けない</t>
@@ -192,14 +192,14 @@
     <rPh sb="23" eb="24">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>乗員</t>
     <rPh sb="0" eb="2">
       <t>ジョウイン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ジョイスティックを前に倒すと前進する</t>
@@ -212,7 +212,7 @@
     <rPh sb="14" eb="16">
       <t>ゼンシン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ジョイスティックを左右に倒すと左右の姿勢が変化する</t>
@@ -231,11 +231,11 @@
     <rPh sb="21" eb="23">
       <t>ヘンカ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ラズパイ</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ジョイスティックの倒し角度に合わせて目標車速が変化する</t>
@@ -257,15 +257,15 @@
     <rPh sb="23" eb="25">
       <t>ヘンカ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プログラムSW</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ギネスモード</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>目標車速上限を○○に変更する</t>
@@ -281,36 +281,26 @@
     <rPh sb="10" eb="12">
       <t>ヘンコウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>コントローラを変更する</t>
     <rPh sb="7" eb="9">
       <t>ヘンコウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ジョイコン</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Microbit</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>DモードからPモードに切り替える</t>
-    <rPh sb="11" eb="12">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>？</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PモードからDモードに切り替えることでメカブレーキが解除される</t>
@@ -323,54 +313,18 @@
     <rPh sb="26" eb="28">
       <t>カイジョ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PKB OFF信号を出力する</t>
-    <rPh sb="7" eb="9">
-      <t>シンゴウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PKB OFF信号を受信する</t>
-    <rPh sb="7" eb="9">
-      <t>シンゴウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジュシン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PKB OFFの時に目標車速を算出する</t>
-    <rPh sb="8" eb="9">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>モクヒョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シャソク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ラズパイGPIO</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バッテリー充電</t>
     <rPh sb="5" eb="7">
       <t>ジュウデン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>異常を検出する</t>
@@ -380,7 +334,7 @@
     <rPh sb="3" eb="5">
       <t>ケンシュツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ジョイスティックを後ろに倒すと後退する</t>
@@ -393,7 +347,7 @@
     <rPh sb="15" eb="17">
       <t>コウタイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>強制停止を出す</t>
@@ -403,18 +357,18 @@
     <rPh sb="5" eb="6">
       <t>ダ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>スフィア評価一覧</t>
     <rPh sb="4" eb="8">
       <t>ヒョウカイチラン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>フェーズ</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>実装チェック　～8/9
@@ -443,7 +397,7 @@
     <rPh sb="53" eb="55">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>台座組付け時（産業用ラズパイ、LMガイド納入後）～9/6
@@ -481,7 +435,7 @@
     <rPh sb="61" eb="62">
       <t>ミ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>球体搭載時、駆動前安全確認　～9/18
@@ -510,7 +464,7 @@
     <rPh sb="39" eb="41">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>走行試験 ～10/10
@@ -536,21 +490,21 @@
     <rPh sb="44" eb="46">
       <t>シア</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
       <t>コウモク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>評価条件・良品条件</t>
@@ -563,28 +517,28 @@
     <rPh sb="5" eb="9">
       <t>リョウヒンジョウケン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>担当</t>
     <rPh sb="0" eb="2">
       <t>タントウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>システム全体</t>
     <rPh sb="4" eb="6">
       <t>ゼンタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>起動</t>
     <rPh sb="0" eb="2">
       <t>キドウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>制御バッテリONで各コンピュータが起動・制御開始</t>
@@ -600,22 +554,22 @@
     <rPh sb="20" eb="24">
       <t>セイギョカイシ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>かとしょー</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>停止</t>
     <rPh sb="0" eb="2">
       <t>テイシ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>IG-ON</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>電源投入後、遠隔操作でＩＧ－ＯＮ状態に遷移</t>
@@ -631,15 +585,15 @@
     <rPh sb="19" eb="21">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>なかおじ</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Rdy-ON</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ＩＧ－ＯＮ状態から、遠隔操作でＲＤＹ－ＯＮ状態に遷移</t>
@@ -655,21 +609,21 @@
     <rPh sb="24" eb="26">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>P⇔D遷移</t>
     <rPh sb="3" eb="5">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>セレクタスイッチによりＰ⇔Ｄ遷移</t>
     <rPh sb="14" eb="16">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>電源関係
@@ -678,14 +632,14 @@
     <rPh sb="0" eb="4">
       <t>デンゲンカンケイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>バッテリ電源</t>
     <rPh sb="4" eb="6">
       <t>デンゲン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>並列駆動バッテリから電力が供給できること</t>
@@ -698,11 +652,11 @@
     <rPh sb="13" eb="15">
       <t>キョウキュウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>うめさん</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>バッテリ通信（単体）</t>
@@ -712,7 +666,7 @@
     <rPh sb="7" eb="9">
       <t>タンタイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>各バッテリと通信ができ、SOCが読めること</t>
@@ -725,14 +679,14 @@
     <rPh sb="16" eb="17">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>バッテリ通信</t>
     <rPh sb="4" eb="6">
       <t>ツウシン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>産業用ラズパイと接続して見られることを確認</t>
@@ -748,7 +702,7 @@
     <rPh sb="19" eb="21">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>制御PF
@@ -756,7 +710,7 @@
     <rPh sb="0" eb="2">
       <t>セイギョ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>全ての制御がコールされ、初期化処理・周期処理ができること</t>
@@ -772,7 +726,7 @@
     <rPh sb="18" eb="22">
       <t>シュウキショリ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>駆動制御
@@ -780,14 +734,14 @@
     <rPh sb="0" eb="4">
       <t>クドウセイギョ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ドライバ通信</t>
     <rPh sb="4" eb="6">
       <t>ツウシン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ELMOの各ドライバが接続できていること</t>
@@ -797,7 +751,7 @@
     <rPh sb="11" eb="13">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>モータ駆動</t>
@@ -809,33 +763,17 @@
     <t>台座のハンチングが抑えられること</t>
   </si>
   <si>
-    <t>駆動指令～応答までの遅れが十分に小さいこと（加速）
-無線コントローラ/ジョイスティックそれぞれ、体感で</t>
-    <rPh sb="26" eb="28">
-      <t>ムセン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>タイカン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ドライバ通信</t>
   </si>
   <si>
     <t>エラー検出ができること</t>
-  </si>
-  <si>
-    <t>駆動指令～応答までの遅れが十分に小さいこと（減速）
-無線コントローラ/ジョイスティックそれぞれ、体感で</t>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>モータ駆動</t>
     <rPh sb="3" eb="5">
       <t>クドウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>全モータを同時に動かせること</t>
@@ -845,7 +783,7 @@
     <rPh sb="18" eb="22">
       <t>カイテンソクド</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>空転しないこと（特別な対処いる？）</t>
@@ -855,7 +793,7 @@
     <rPh sb="3" eb="5">
       <t>ニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>車速信号が取得できること</t>
@@ -868,7 +806,7 @@
     <rPh sb="5" eb="7">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>停止操作中はモータ停止状態が維持できること</t>
@@ -882,14 +820,14 @@
     <rPh sb="0" eb="4">
       <t>ジュウシンセイギョ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>９軸センサ</t>
     <rPh sb="1" eb="2">
       <t>ジク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>必要な情報を取得できていること</t>
@@ -902,7 +840,7 @@
     <rPh sb="6" eb="8">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>安全機能
@@ -910,25 +848,25 @@
     <rPh sb="0" eb="4">
       <t>アンゼンキノウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>メインリレー</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ラズパイからの制御でON/OFFできること</t>
     <rPh sb="7" eb="9">
       <t>セイギョ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>緊急遮断</t>
     <rPh sb="0" eb="4">
       <t>キンキュウシャダン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>駆動電源が遮断されること</t>
@@ -938,7 +876,7 @@
     <rPh sb="5" eb="7">
       <t>シャダン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>駆動系異常検知</t>
@@ -954,7 +892,7 @@
     <rPh sb="5" eb="7">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>モータ・インバーター障害、通信路障害の検知</t>
@@ -973,7 +911,7 @@
     <rPh sb="19" eb="21">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>操作系異常検知</t>
@@ -989,7 +927,7 @@
     <rPh sb="5" eb="7">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ジョイスティック障害、通信路障害の検知</t>
@@ -1002,7 +940,7 @@
     <rPh sb="14" eb="16">
       <t>ショウガイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>無線通信機能(正常系)</t>
@@ -1018,7 +956,7 @@
     <rPh sb="7" eb="10">
       <t>セイジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>監視用PCとの無線通信</t>
@@ -1031,7 +969,7 @@
     <rPh sb="9" eb="11">
       <t>ツウシン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>無線通信系異常検知</t>
@@ -1050,7 +988,7 @@
     <rPh sb="7" eb="9">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>無線通信途絶の検知</t>
@@ -1066,7 +1004,7 @@
     <rPh sb="7" eb="9">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>メインマイコン異常検知</t>
@@ -1076,7 +1014,7 @@
     <rPh sb="9" eb="11">
       <t>ケンチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>メインプロセス・OSのフリーズ、異常終了の検知(WatchDogを使うため産業用ラズパイ入荷以降)</t>
@@ -1098,16 +1036,16 @@
     <rPh sb="46" eb="48">
       <t>イコウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ユーザIF
 たにぐさん</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>ジョイスティック</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>前後・左右方向の情報が取れること</t>
@@ -1126,11 +1064,11 @@
     <rPh sb="11" eb="12">
       <t>ト</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>たにぐさん</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>冗長化した状態でセンサ値取得ができ、キャリブレーションが完了していること。</t>
@@ -1148,6 +1086,113 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>セレクタ情報を出力する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>セレクタ情報を受信する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジュシン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>駆動指令～応答までの遅れが体感で十分に小さいこと</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>DモードからPモードに切り替えることでメカブレーキが作動する</t>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>セレクタ情報がPモードの時にはジョイスティック入力を禁止する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>セレクタ情報がDモードの時にはジョイスティック入力を許可する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キョカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>現在車速と目標車速の差から目標加速度を算出する</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンザイシャソク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シャソク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>現在車速を取得する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シャソク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュトク</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1156,12 +1201,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1484,174 +1537,171 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="12" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="13" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="14" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="15" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="12" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="16" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2037,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H44"/>
+  <dimension ref="A2:H48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
@@ -2063,14 +2113,14 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -2165,194 +2215,201 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
         <v>24</v>
       </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C17" s="3"/>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="F25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="C26" s="3"/>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="C29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B31" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="C33" s="3"/>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B35" s="3"/>
-      <c r="C35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
+      <c r="C35" s="3"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E36" t="s">
-        <v>22</v>
+      <c r="D36" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B41" s="3"/>
@@ -2370,8 +2427,24 @@
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
     </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2400,939 +2473,935 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="4" spans="2:14" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+    </row>
+    <row r="5" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13" t="s">
+      <c r="E5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-    </row>
-    <row r="5" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="15" t="s">
+      <c r="F5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B6" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="17" t="s">
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B7" s="44"/>
+      <c r="C7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B8" s="44"/>
+      <c r="C8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="25"/>
-      <c r="C7" s="26" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B9" s="44"/>
+      <c r="C9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26" t="s">
+      <c r="D9" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="25"/>
-      <c r="C8" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="30" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B10" s="44"/>
+      <c r="C10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="D10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B9" s="25"/>
-      <c r="C9" s="30" t="s">
+      <c r="E10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="45"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B12" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="C12" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B10" s="25"/>
-      <c r="C10" s="26" t="s">
+      <c r="D12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="E12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-    </row>
-    <row r="11" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="36" t="s">
+      <c r="F12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B13" s="44"/>
+      <c r="C13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="D13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="E13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="G13" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26" t="s">
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B14" s="44"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B15" s="44"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+    </row>
+    <row r="16" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="45"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B17" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="27" t="s">
+      <c r="E17" s="25"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B18" s="44"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B19" s="44"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B20" s="44"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+    </row>
+    <row r="21" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="45"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+    </row>
+    <row r="22" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="C22" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-    </row>
-    <row r="16" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="36" t="s">
+      <c r="D22" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37" t="s">
+      <c r="E22" s="12"/>
+      <c r="F22" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-    </row>
-    <row r="21" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-    </row>
-    <row r="22" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="36" t="s">
+      <c r="J22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="K22" s="14"/>
+      <c r="L22" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B23" s="46"/>
+      <c r="C23" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="23" t="s">
+      <c r="G23" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="N23" s="31"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B24" s="44"/>
+      <c r="C24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="M22" s="24" t="s">
+      <c r="G24" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="24"/>
-    </row>
-    <row r="23" spans="2:14" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="43" t="s">
+      <c r="H24" s="17"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B25" s="44"/>
+      <c r="C25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="43"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="M23" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="N23" s="45"/>
-    </row>
-    <row r="24" spans="2:14" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B24" s="25"/>
-      <c r="C24" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="27" t="s">
+      <c r="H25" s="17"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B26" s="44"/>
+      <c r="C26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B27" s="44"/>
+      <c r="C27" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="25"/>
-      <c r="C25" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="26" t="s">
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B28" s="44"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B29" s="44"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B30" s="44"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+    </row>
+    <row r="31" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="45"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B32" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="27" t="s">
+      <c r="C32" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="25"/>
-      <c r="C26" s="26" t="s">
+      <c r="D32" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="E32" s="25"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B33" s="44"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B34" s="44"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+    </row>
+    <row r="35" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="45"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B36" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="25"/>
-      <c r="C27" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="26" t="s">
+      <c r="C36" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="25"/>
-      <c r="C28" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="26" t="s">
+      <c r="D36" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="25"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B30" s="25"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-    </row>
-    <row r="31" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="31"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B32" s="36" t="s">
+      <c r="E36" s="25"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="36"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B37" s="44"/>
+      <c r="C37" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="D37" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="E37" s="16"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="37"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B38" s="44"/>
+      <c r="C38" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="37"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B33" s="25"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-    </row>
-    <row r="35" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="31"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B36" s="36" t="s">
+      <c r="D38" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="E38" s="16"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="37"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B39" s="44"/>
+      <c r="C39" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D39" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="51"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B37" s="25"/>
-      <c r="C37" s="26" t="s">
+      <c r="E39" s="16"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="37"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B40" s="44"/>
+      <c r="C40" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D40" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="52"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B38" s="25"/>
-      <c r="C38" s="26" t="s">
+      <c r="E40" s="32"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="38"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B41" s="44"/>
+      <c r="C41" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D41" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="52"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B39" s="25"/>
-      <c r="C39" s="26" t="s">
+      <c r="E41" s="32"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="38"/>
+    </row>
+    <row r="42" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="45"/>
+      <c r="C42" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D42" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="52"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B40" s="25"/>
-      <c r="C40" s="30" t="s">
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="41"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B43" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="C43" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="53"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B41" s="25"/>
-      <c r="C41" s="54" t="s">
+      <c r="D43" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="E43" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="47"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="53"/>
-    </row>
-    <row r="42" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="31"/>
-      <c r="C42" s="55" t="s">
+      <c r="F43" s="29"/>
+      <c r="G43" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="56"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B43" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="H43" s="43"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
-      <c r="N43" s="45"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B44" s="25"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B46" s="25"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B48" s="25"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B50" s="25"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="29"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
     </row>
     <row r="51" spans="2:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="23"/>
+      <c r="K51" s="23"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="B6:B11"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="B22:B31"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="B36:B42"/>
     <mergeCell ref="B43:B51"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="B12:B16"/>
   </mergeCells>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3347,16 +3416,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0e6d3778-a5a9-462e-9535-d62feef6a121">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010076513F2C256FD046AEF78162D32B3F62" ma:contentTypeVersion="14" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="46169733afdbd58148a44cd3e1925b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc322cb2-fd5f-4ab7-a896-0baeea657d4d" xmlns:ns3="0e6d3778-a5a9-462e-9535-d62feef6a121" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00a9778a20c67567d2cc137aa4f20099" ns2:_="" ns3:_="">
     <xsd:import namespace="fc322cb2-fd5f-4ab7-a896-0baeea657d4d"/>
@@ -3579,6 +3638,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0e6d3778-a5a9-462e-9535-d62feef6a121">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FEE2DBF-551A-48CE-B68B-D795D765734E}">
   <ds:schemaRefs>
@@ -3588,23 +3657,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54575948-74A6-47AE-AF4D-92F3E5CE6564}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fc322cb2-fd5f-4ab7-a896-0baeea657d4d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0e6d3778-a5a9-462e-9535-d62feef6a121"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D6ABE8A-A251-4B04-AAD8-C8A954DA36E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3621,4 +3673,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54575948-74A6-47AE-AF4D-92F3E5CE6564}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fc322cb2-fd5f-4ab7-a896-0baeea657d4d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0e6d3778-a5a9-462e-9535-d62feef6a121"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>